--- a/diseases/d108/2000-2004.xlsx
+++ b/diseases/d108/2000-2004.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>2</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0.03863837217310803</v>
       </c>
@@ -1309,9 +1306,6 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -1705,9 +1699,6 @@
       <c r="O7" t="n">
         <v>1</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0.02226741517840542</v>
       </c>
@@ -2249,9 +2240,6 @@
       <c r="O10" t="n">
         <v>2</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.03863837217310803</v>
       </c>
@@ -2645,9 +2633,6 @@
       <c r="O12" t="n">
         <v>3</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.06680224553521626</v>
       </c>
@@ -3189,9 +3174,6 @@
       <c r="O15" t="n">
         <v>1</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0.01931918608655401</v>
       </c>
@@ -3585,9 +3567,6 @@
       <c r="O17" t="n">
         <v>2</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0.04453483035681084</v>
       </c>
@@ -4129,9 +4108,6 @@
       <c r="O20" t="n">
         <v>1</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.01931918608655401</v>
       </c>
@@ -4525,9 +4501,6 @@
       <c r="O22" t="n">
         <v>2</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0.04453483035681084</v>
       </c>
@@ -5069,9 +5042,6 @@
       <c r="O25" t="n">
         <v>2</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0.03863837217310803</v>
       </c>
@@ -5465,9 +5435,6 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -6009,9 +5976,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -6405,9 +6369,6 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
@@ -6949,9 +6910,6 @@
       <c r="O35" t="n">
         <v>1</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0.01931918608655401</v>
       </c>
@@ -7345,9 +7303,6 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
@@ -7889,9 +7844,6 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
@@ -8285,9 +8237,6 @@
       <c r="O42" t="n">
         <v>1</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0.02226741517840542</v>
       </c>
@@ -8829,9 +8778,6 @@
       <c r="O45" t="n">
         <v>1</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0.01931918608655401</v>
       </c>
@@ -9225,9 +9171,6 @@
       <c r="O47" t="n">
         <v>1</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0.02226741517840542</v>
       </c>
@@ -9769,9 +9712,6 @@
       <c r="O50" t="n">
         <v>4</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.07727674434621605</v>
       </c>
@@ -10165,9 +10105,6 @@
       <c r="O52" t="n">
         <v>3</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0.06680224553521626</v>
       </c>
@@ -10709,9 +10646,6 @@
       <c r="O55" t="n">
         <v>4</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0.07727674434621605</v>
       </c>
@@ -11105,9 +11039,6 @@
       <c r="O57" t="n">
         <v>3</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0.06680224553521626</v>
       </c>
@@ -11649,9 +11580,6 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
@@ -12045,9 +11973,6 @@
       <c r="O62" t="n">
         <v>2</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.04453483035681084</v>
       </c>
@@ -12589,9 +12514,6 @@
       <c r="O65" t="n">
         <v>5</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0.09637679162046203</v>
       </c>
@@ -12985,9 +12907,6 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
@@ -13381,9 +13300,6 @@
       <c r="O69" t="n">
         <v>2</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0.04430996861303373</v>
       </c>
@@ -13925,9 +13841,6 @@
       <c r="O72" t="n">
         <v>1</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.01927535832409241</v>
       </c>
@@ -14321,9 +14234,6 @@
       <c r="O74" t="n">
         <v>2</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.04430996861303373</v>
       </c>
@@ -14865,9 +14775,6 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
@@ -15261,9 +15168,6 @@
       <c r="O79" t="n">
         <v>1</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0.02215498430651687</v>
       </c>
@@ -15805,9 +15709,6 @@
       <c r="O82" t="n">
         <v>3</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.05782607497227721</v>
       </c>
@@ -16201,9 +16102,6 @@
       <c r="O84" t="n">
         <v>2</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0.04430996861303373</v>
       </c>
@@ -16745,9 +16643,6 @@
       <c r="O87" t="n">
         <v>3</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0.05782607497227721</v>
       </c>
@@ -17141,9 +17036,6 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
@@ -17685,9 +17577,6 @@
       <c r="O92" t="n">
         <v>0</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0</v>
       </c>
@@ -18081,9 +17970,6 @@
       <c r="O94" t="n">
         <v>1</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0.02215498430651687</v>
       </c>
@@ -18625,9 +18511,6 @@
       <c r="O97" t="n">
         <v>1</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0.01927535832409241</v>
       </c>
@@ -19021,9 +18904,6 @@
       <c r="O99" t="n">
         <v>1</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0.02215498430651687</v>
       </c>
@@ -19565,9 +19445,6 @@
       <c r="O102" t="n">
         <v>6</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0.1156521499445544</v>
       </c>
@@ -19961,9 +19838,6 @@
       <c r="O104" t="n">
         <v>1</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.02215498430651687</v>
       </c>
@@ -20505,9 +20379,6 @@
       <c r="O107" t="n">
         <v>3</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.05782607497227721</v>
       </c>
@@ -20901,9 +20772,6 @@
       <c r="O109" t="n">
         <v>2</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0.04430996861303373</v>
       </c>
@@ -21445,9 +21313,6 @@
       <c r="O112" t="n">
         <v>3</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0.05782607497227721</v>
       </c>
@@ -21841,9 +21706,6 @@
       <c r="O114" t="n">
         <v>1</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.02215498430651687</v>
       </c>
@@ -22385,9 +22247,6 @@
       <c r="O117" t="n">
         <v>4</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0.07710143329636962</v>
       </c>
@@ -22781,9 +22640,6 @@
       <c r="O119" t="n">
         <v>1</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0.02215498430651687</v>
       </c>
@@ -23325,9 +23181,6 @@
       <c r="O122" t="n">
         <v>0</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0</v>
       </c>
@@ -23721,9 +23574,6 @@
       <c r="O124" t="n">
         <v>2</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0.04430996861303373</v>
       </c>
@@ -24265,9 +24115,6 @@
       <c r="O127" t="n">
         <v>4</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0.07691500084798789</v>
       </c>
@@ -24661,9 +24508,6 @@
       <c r="O129" t="n">
         <v>0</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0</v>
       </c>
@@ -25057,9 +24901,6 @@
       <c r="O131" t="n">
         <v>4</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0.08814428514323666</v>
       </c>
@@ -25601,9 +25442,6 @@
       <c r="O134" t="n">
         <v>2</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0.03845750042399394</v>
       </c>
@@ -25997,9 +25835,6 @@
       <c r="O136" t="n">
         <v>3</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0.0661082138574275</v>
       </c>
@@ -26541,9 +26376,6 @@
       <c r="O139" t="n">
         <v>0</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0</v>
       </c>
@@ -26937,9 +26769,6 @@
       <c r="O141" t="n">
         <v>0</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>0</v>
       </c>
@@ -27481,9 +27310,6 @@
       <c r="O144" t="n">
         <v>1</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0.01922875021199697</v>
       </c>
@@ -27877,9 +27703,6 @@
       <c r="O146" t="n">
         <v>0</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0</v>
       </c>
@@ -28421,9 +28244,6 @@
       <c r="O149" t="n">
         <v>1</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0.01922875021199697</v>
       </c>
@@ -28817,9 +28637,6 @@
       <c r="O151" t="n">
         <v>0</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0</v>
       </c>
@@ -29361,9 +29178,6 @@
       <c r="O154" t="n">
         <v>1</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0.01922875021199697</v>
       </c>
@@ -29757,9 +29571,6 @@
       <c r="O156" t="n">
         <v>2</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0.04407214257161833</v>
       </c>
@@ -30301,9 +30112,6 @@
       <c r="O159" t="n">
         <v>2</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>0.03845750042399394</v>
       </c>
@@ -30697,9 +30505,6 @@
       <c r="O161" t="n">
         <v>3</v>
       </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
       <c r="R161" t="n">
         <v>0.0661082138574275</v>
       </c>
@@ -31241,9 +31046,6 @@
       <c r="O164" t="n">
         <v>2</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0.03845750042399394</v>
       </c>
@@ -31637,9 +31439,6 @@
       <c r="O166" t="n">
         <v>1</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0.02203607128580917</v>
       </c>
@@ -32181,9 +31980,6 @@
       <c r="O169" t="n">
         <v>3</v>
       </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
       <c r="R169" t="n">
         <v>0.05768625063599091</v>
       </c>
@@ -32577,9 +32373,6 @@
       <c r="O171" t="n">
         <v>3</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>0.0661082138574275</v>
       </c>
@@ -33121,9 +32914,6 @@
       <c r="O174" t="n">
         <v>2</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>0.03845750042399394</v>
       </c>
@@ -33517,9 +33307,6 @@
       <c r="O176" t="n">
         <v>3</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>0.0661082138574275</v>
       </c>
@@ -34061,9 +33848,6 @@
       <c r="O179" t="n">
         <v>0</v>
       </c>
-      <c r="Q179" t="n">
-        <v>0</v>
-      </c>
       <c r="R179" t="n">
         <v>0</v>
       </c>
@@ -34457,9 +34241,6 @@
       <c r="O181" t="n">
         <v>0</v>
       </c>
-      <c r="Q181" t="n">
-        <v>0</v>
-      </c>
       <c r="R181" t="n">
         <v>0</v>
       </c>
@@ -35001,9 +34782,6 @@
       <c r="O184" t="n">
         <v>2</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>0.03845750042399394</v>
       </c>
@@ -35397,9 +35175,6 @@
       <c r="O186" t="n">
         <v>2</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0.04407214257161833</v>
       </c>
@@ -35941,9 +35716,6 @@
       <c r="O189" t="n">
         <v>2</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>0.03836595558565152</v>
       </c>
@@ -36337,9 +36109,6 @@
       <c r="O191" t="n">
         <v>0</v>
       </c>
-      <c r="Q191" t="n">
-        <v>0</v>
-      </c>
       <c r="R191" t="n">
         <v>0</v>
       </c>
@@ -36733,9 +36502,6 @@
       <c r="O193" t="n">
         <v>1</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0.02190739350432638</v>
       </c>
@@ -37277,9 +37043,6 @@
       <c r="O196" t="n">
         <v>2</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>0.03836595558565152</v>
       </c>
@@ -37673,9 +37436,6 @@
       <c r="O198" t="n">
         <v>0</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>0</v>
       </c>
@@ -38217,9 +37977,6 @@
       <c r="O201" t="n">
         <v>5</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="R201" t="n">
         <v>0.09591488896412878</v>
       </c>
@@ -38613,9 +38370,6 @@
       <c r="O203" t="n">
         <v>4</v>
       </c>
-      <c r="Q203" t="n">
-        <v>0</v>
-      </c>
       <c r="R203" t="n">
         <v>0.08762957401730553</v>
       </c>
@@ -39157,9 +38911,6 @@
       <c r="O206" t="n">
         <v>4</v>
       </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
       <c r="R206" t="n">
         <v>0.07673191117130304</v>
       </c>
@@ -39553,9 +39304,6 @@
       <c r="O208" t="n">
         <v>1</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>0.02190739350432638</v>
       </c>
@@ -40097,9 +39845,6 @@
       <c r="O211" t="n">
         <v>2</v>
       </c>
-      <c r="Q211" t="n">
-        <v>0</v>
-      </c>
       <c r="R211" t="n">
         <v>0.03836595558565152</v>
       </c>
@@ -40493,9 +40238,6 @@
       <c r="O213" t="n">
         <v>1</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="R213" t="n">
         <v>0.02190739350432638</v>
       </c>
@@ -41037,9 +40779,6 @@
       <c r="O216" t="n">
         <v>0</v>
       </c>
-      <c r="Q216" t="n">
-        <v>0</v>
-      </c>
       <c r="R216" t="n">
         <v>0</v>
       </c>
@@ -41433,9 +41172,6 @@
       <c r="O218" t="n">
         <v>0</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>0</v>
       </c>
@@ -41977,9 +41713,6 @@
       <c r="O221" t="n">
         <v>4</v>
       </c>
-      <c r="Q221" t="n">
-        <v>0</v>
-      </c>
       <c r="R221" t="n">
         <v>0.07673191117130304</v>
       </c>
@@ -42373,9 +42106,6 @@
       <c r="O223" t="n">
         <v>2</v>
       </c>
-      <c r="Q223" t="n">
-        <v>0</v>
-      </c>
       <c r="R223" t="n">
         <v>0.04381478700865277</v>
       </c>
@@ -42917,9 +42647,6 @@
       <c r="O226" t="n">
         <v>6</v>
       </c>
-      <c r="Q226" t="n">
-        <v>0</v>
-      </c>
       <c r="R226" t="n">
         <v>0.1150978667569545</v>
       </c>
@@ -43313,9 +43040,6 @@
       <c r="O228" t="n">
         <v>1</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="R228" t="n">
         <v>0.02190739350432638</v>
       </c>
@@ -43857,9 +43581,6 @@
       <c r="O231" t="n">
         <v>7</v>
       </c>
-      <c r="Q231" t="n">
-        <v>0</v>
-      </c>
       <c r="R231" t="n">
         <v>0.1342808445497803</v>
       </c>
@@ -44253,9 +43974,6 @@
       <c r="O233" t="n">
         <v>0</v>
       </c>
-      <c r="Q233" t="n">
-        <v>0</v>
-      </c>
       <c r="R233" t="n">
         <v>0</v>
       </c>
@@ -44797,9 +44515,6 @@
       <c r="O236" t="n">
         <v>3</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="R236" t="n">
         <v>0.05754893337847727</v>
       </c>
@@ -45193,9 +44908,6 @@
       <c r="O238" t="n">
         <v>1</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="R238" t="n">
         <v>0.02190739350432638</v>
       </c>
@@ -45737,9 +45449,6 @@
       <c r="O241" t="n">
         <v>4</v>
       </c>
-      <c r="Q241" t="n">
-        <v>0</v>
-      </c>
       <c r="R241" t="n">
         <v>0.07673191117130304</v>
       </c>
@@ -46133,9 +45842,6 @@
       <c r="O243" t="n">
         <v>2</v>
       </c>
-      <c r="Q243" t="n">
-        <v>0</v>
-      </c>
       <c r="R243" t="n">
         <v>0.04381478700865277</v>
       </c>
@@ -46677,9 +46383,6 @@
       <c r="O246" t="n">
         <v>3</v>
       </c>
-      <c r="Q246" t="n">
-        <v>0</v>
-      </c>
       <c r="R246" t="n">
         <v>0.05754893337847727</v>
       </c>
@@ -47073,9 +46776,6 @@
       <c r="O248" t="n">
         <v>3</v>
       </c>
-      <c r="Q248" t="n">
-        <v>0</v>
-      </c>
       <c r="R248" t="n">
         <v>0.06572218051297914</v>
       </c>
@@ -47617,9 +47317,6 @@
       <c r="O251" t="n">
         <v>1</v>
       </c>
-      <c r="Q251" t="n">
-        <v>0</v>
-      </c>
       <c r="R251" t="n">
         <v>0.01912723205234435</v>
       </c>
@@ -48013,9 +47710,6 @@
       <c r="O253" t="n">
         <v>1</v>
       </c>
-      <c r="Q253" t="n">
-        <v>0</v>
-      </c>
       <c r="R253" t="n">
         <v>0.3422682458923532</v>
       </c>
@@ -48409,9 +48103,6 @@
       <c r="O255" t="n">
         <v>3</v>
       </c>
-      <c r="Q255" t="n">
-        <v>0</v>
-      </c>
       <c r="R255" t="n">
         <v>0.06533467414603497</v>
       </c>
@@ -48953,9 +48644,6 @@
       <c r="O258" t="n">
         <v>3</v>
       </c>
-      <c r="Q258" t="n">
-        <v>0</v>
-      </c>
       <c r="R258" t="n">
         <v>0.05738169615703305</v>
       </c>
@@ -49349,9 +49037,6 @@
       <c r="O260" t="n">
         <v>3</v>
       </c>
-      <c r="Q260" t="n">
-        <v>0</v>
-      </c>
       <c r="R260" t="n">
         <v>0.06533467414603497</v>
       </c>
@@ -49893,9 +49578,6 @@
       <c r="O263" t="n">
         <v>0</v>
       </c>
-      <c r="Q263" t="n">
-        <v>0</v>
-      </c>
       <c r="R263" t="n">
         <v>0</v>
       </c>
@@ -50289,9 +49971,6 @@
       <c r="O265" t="n">
         <v>1</v>
       </c>
-      <c r="Q265" t="n">
-        <v>0</v>
-      </c>
       <c r="R265" t="n">
         <v>0.02177822471534499</v>
       </c>
@@ -50833,9 +50512,6 @@
       <c r="O268" t="n">
         <v>3</v>
       </c>
-      <c r="Q268" t="n">
-        <v>0</v>
-      </c>
       <c r="R268" t="n">
         <v>0.05738169615703305</v>
       </c>
@@ -51229,9 +50905,6 @@
       <c r="O270" t="n">
         <v>1</v>
       </c>
-      <c r="Q270" t="n">
-        <v>0</v>
-      </c>
       <c r="R270" t="n">
         <v>0.02177822471534499</v>
       </c>
@@ -51773,9 +51446,6 @@
       <c r="O273" t="n">
         <v>1</v>
       </c>
-      <c r="Q273" t="n">
-        <v>0</v>
-      </c>
       <c r="R273" t="n">
         <v>0.01912723205234435</v>
       </c>
@@ -52169,9 +51839,6 @@
       <c r="O275" t="n">
         <v>0</v>
       </c>
-      <c r="Q275" t="n">
-        <v>0</v>
-      </c>
       <c r="R275" t="n">
         <v>0</v>
       </c>
@@ -52713,9 +52380,6 @@
       <c r="O278" t="n">
         <v>5</v>
       </c>
-      <c r="Q278" t="n">
-        <v>0</v>
-      </c>
       <c r="R278" t="n">
         <v>0.09563616026172174</v>
       </c>
@@ -53109,9 +52773,6 @@
       <c r="O280" t="n">
         <v>4</v>
       </c>
-      <c r="Q280" t="n">
-        <v>0</v>
-      </c>
       <c r="R280" t="n">
         <v>0.08711289886137998</v>
       </c>
@@ -53653,9 +53314,6 @@
       <c r="O283" t="n">
         <v>7</v>
       </c>
-      <c r="Q283" t="n">
-        <v>0</v>
-      </c>
       <c r="R283" t="n">
         <v>0.1338906243664104</v>
       </c>
@@ -54049,9 +53707,6 @@
       <c r="O285" t="n">
         <v>2</v>
       </c>
-      <c r="Q285" t="n">
-        <v>0</v>
-      </c>
       <c r="R285" t="n">
         <v>0.04355644943068999</v>
       </c>
@@ -54593,9 +54248,6 @@
       <c r="O288" t="n">
         <v>3</v>
       </c>
-      <c r="Q288" t="n">
-        <v>0</v>
-      </c>
       <c r="R288" t="n">
         <v>0.05738169615703305</v>
       </c>
@@ -54989,9 +54641,6 @@
       <c r="O290" t="n">
         <v>1</v>
       </c>
-      <c r="Q290" t="n">
-        <v>0</v>
-      </c>
       <c r="R290" t="n">
         <v>0.02177822471534499</v>
       </c>
@@ -55533,9 +55182,6 @@
       <c r="O293" t="n">
         <v>3</v>
       </c>
-      <c r="Q293" t="n">
-        <v>0</v>
-      </c>
       <c r="R293" t="n">
         <v>0.05738169615703305</v>
       </c>
@@ -55929,9 +55575,6 @@
       <c r="O295" t="n">
         <v>3</v>
       </c>
-      <c r="Q295" t="n">
-        <v>0</v>
-      </c>
       <c r="R295" t="n">
         <v>0.06533467414603497</v>
       </c>
@@ -56473,9 +56116,6 @@
       <c r="O298" t="n">
         <v>2</v>
       </c>
-      <c r="Q298" t="n">
-        <v>0</v>
-      </c>
       <c r="R298" t="n">
         <v>0.0382544641046887</v>
       </c>
@@ -56869,9 +56509,6 @@
       <c r="O300" t="n">
         <v>1</v>
       </c>
-      <c r="Q300" t="n">
-        <v>0</v>
-      </c>
       <c r="R300" t="n">
         <v>0.02177822471534499</v>
       </c>
@@ -57413,9 +57050,6 @@
       <c r="O303" t="n">
         <v>2</v>
       </c>
-      <c r="Q303" t="n">
-        <v>0</v>
-      </c>
       <c r="R303" t="n">
         <v>0.0382544641046887</v>
       </c>
@@ -57809,9 +57443,6 @@
       <c r="O305" t="n">
         <v>3</v>
       </c>
-      <c r="Q305" t="n">
-        <v>0</v>
-      </c>
       <c r="R305" t="n">
         <v>0.06533467414603497</v>
       </c>
@@ -58353,9 +57984,6 @@
       <c r="O308" t="n">
         <v>5</v>
       </c>
-      <c r="Q308" t="n">
-        <v>0</v>
-      </c>
       <c r="R308" t="n">
         <v>0.09563616026172174</v>
       </c>
@@ -58748,9 +58376,6 @@
       </c>
       <c r="O310" t="n">
         <v>1</v>
-      </c>
-      <c r="Q310" t="n">
-        <v>0</v>
       </c>
       <c r="R310" t="n">
         <v>0.02177822471534499</v>
